--- a/docs/[13조]_400. 서비스_분석 설계서_432_데이터베이스설계서_v0.1.filled.xlsx
+++ b/docs/[13조]_400. 서비스_분석 설계서_432_데이터베이스설계서_v0.1.filled.xlsx
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H4" s="51" t="inlineStr">
         <is>
-          <t>13 (145 컬럼) // &lt; 1MB (W5 기준 초기)</t>
+          <t>13 (146 컬럼) // &lt; 1MB (W5 기준 초기)</t>
         </is>
       </c>
     </row>

--- a/docs/[13조]_400. 서비스_분석 설계서_432_데이터베이스설계서_v0.1.filled.xlsx
+++ b/docs/[13조]_400. 서비스_분석 설계서_432_데이터베이스설계서_v0.1.filled.xlsx
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H4" s="51" t="inlineStr">
         <is>
-          <t>13 (146 컬럼) // &lt; 1MB (W5 기준 초기)</t>
+          <t>13 (145 컬럼) // &lt; 1MB (W5 기준 초기)</t>
         </is>
       </c>
     </row>
